--- a/Publications.xlsx
+++ b/Publications.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Till\Repositories\GitHub\academic_website\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1236BF7E-0ACB-4779-A71B-E842823AD152}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B132380-9A4B-40AA-928E-B01BCD36EC82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{943F45D4-8764-4040-A091-0C00697455C7}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{943F45D4-8764-4040-A091-0C00697455C7}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -71,9 +71,6 @@
     <t>Journal/Outlet</t>
   </si>
   <si>
-    <t>Richstein, J. C., . . . , Köveker, T., ..., Winkler, J.</t>
-  </si>
-  <si>
     <t>https://doi.org/10.1016/j.joule.2024.11.003</t>
   </si>
   <si>
@@ -318,6 +315,9 @@
   </si>
   <si>
     <t>ExportsCBAM</t>
+  </si>
+  <si>
+    <t>Richstein, J. C., Anatolitis, V., Blömer, R., Bunnenberg, L., Dürrwächter, J., Eckstein, J., Ehrhart, K. M., Friedrichsen, N., Köveker, T., Lehmann, S., Lösch, O., Matthes, F. C., Neuhoff, K., Niemöller, P., Riemer, M., Ueckerdt, F., Wachsmuth, J., Wang, R., Winkler, J.</t>
   </si>
 </sst>
 </file>
@@ -721,13 +721,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>2</v>
@@ -739,49 +739,49 @@
         <v>10</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J1" s="2" t="s">
         <v>6</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="L1" s="2" t="s">
         <v>9</v>
       </c>
       <c r="M1" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="N1" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="O1" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="P1" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="Q1" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="R1" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="S1" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="T1" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="U1" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="U1" s="2" t="s">
+      <c r="V1" s="2" t="s">
         <v>78</v>
-      </c>
-      <c r="V1" s="2" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.35">
@@ -789,7 +789,7 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C2" t="s">
         <v>8</v>
@@ -798,16 +798,16 @@
         <v>2024</v>
       </c>
       <c r="F2" t="s">
+        <v>93</v>
+      </c>
+      <c r="G2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="L2" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="G2" t="s">
-        <v>14</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.35">
@@ -815,25 +815,25 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E3">
         <v>2023</v>
       </c>
       <c r="F3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L3" s="1" t="s">
         <v>15</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.35">
@@ -841,31 +841,31 @@
         <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E4">
         <v>2025</v>
       </c>
       <c r="F4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M4" t="s">
+        <v>66</v>
+      </c>
+      <c r="N4" s="1" t="s">
         <v>67</v>
-      </c>
-      <c r="N4" s="1" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.35">
@@ -873,25 +873,25 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E5">
         <v>2025</v>
       </c>
       <c r="F5" t="s">
+        <v>21</v>
+      </c>
+      <c r="G5" t="s">
+        <v>19</v>
+      </c>
+      <c r="I5" t="s">
+        <v>80</v>
+      </c>
+      <c r="J5" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="G5" t="s">
-        <v>20</v>
-      </c>
-      <c r="I5" t="s">
-        <v>81</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.35">
@@ -899,25 +899,25 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E6">
         <v>2025</v>
       </c>
       <c r="F6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G6" t="s">
+        <v>19</v>
+      </c>
+      <c r="I6" t="s">
+        <v>81</v>
+      </c>
+      <c r="J6" s="1" t="s">
         <v>27</v>
-      </c>
-      <c r="G6" t="s">
-        <v>20</v>
-      </c>
-      <c r="I6" t="s">
-        <v>82</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.35">
@@ -925,25 +925,25 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E7">
         <v>2025</v>
       </c>
       <c r="F7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I7" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.35">
@@ -951,31 +951,31 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E8">
         <v>2025</v>
       </c>
       <c r="F8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G8" t="s">
+        <v>46</v>
+      </c>
+      <c r="H8" t="s">
         <v>47</v>
       </c>
-      <c r="H8" t="s">
-        <v>48</v>
-      </c>
       <c r="J8" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.35">
@@ -983,31 +983,31 @@
         <v>5</v>
       </c>
       <c r="B9" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E9">
         <v>2025</v>
       </c>
       <c r="F9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G9" t="s">
+        <v>46</v>
+      </c>
+      <c r="H9" t="s">
         <v>47</v>
       </c>
-      <c r="H9" t="s">
-        <v>48</v>
-      </c>
       <c r="J9" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.35">
@@ -1015,22 +1015,22 @@
         <v>5</v>
       </c>
       <c r="B10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C10" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E10">
         <v>2025</v>
       </c>
       <c r="F10" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G10" t="s">
+        <v>48</v>
+      </c>
+      <c r="J10" s="1" t="s">
         <v>49</v>
-      </c>
-      <c r="J10" s="1" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.35">
@@ -1038,31 +1038,31 @@
         <v>5</v>
       </c>
       <c r="B11" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C11" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E11">
         <v>2024</v>
       </c>
       <c r="F11" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G11" t="s">
+        <v>46</v>
+      </c>
+      <c r="H11" t="s">
         <v>47</v>
       </c>
-      <c r="H11" t="s">
-        <v>48</v>
-      </c>
       <c r="J11" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.35">
@@ -1070,22 +1070,22 @@
         <v>5</v>
       </c>
       <c r="B12" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C12" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E12">
         <v>2023</v>
       </c>
       <c r="F12" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G12" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.35">
@@ -1093,31 +1093,31 @@
         <v>5</v>
       </c>
       <c r="B13" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C13" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D13" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E13">
         <v>2022</v>
       </c>
       <c r="F13" t="s">
+        <v>58</v>
+      </c>
+      <c r="G13" t="s">
+        <v>46</v>
+      </c>
+      <c r="H13" t="s">
+        <v>47</v>
+      </c>
+      <c r="J13" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="G13" t="s">
-        <v>47</v>
-      </c>
-      <c r="H13" t="s">
-        <v>48</v>
-      </c>
-      <c r="J13" s="1" t="s">
-        <v>60</v>
-      </c>
       <c r="K13" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.35">
@@ -1125,22 +1125,22 @@
         <v>5</v>
       </c>
       <c r="B14" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C14" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E14">
         <v>2022</v>
       </c>
       <c r="F14" t="s">
+        <v>62</v>
+      </c>
+      <c r="G14" t="s">
         <v>63</v>
       </c>
-      <c r="G14" t="s">
+      <c r="J14" s="1" t="s">
         <v>64</v>
-      </c>
-      <c r="J14" s="1" t="s">
-        <v>65</v>
       </c>
     </row>
   </sheetData>
